--- a/策划案.xlsx
+++ b/策划案.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\By GitHub\Twenty-four\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF2F7AA5-579C-4DF3-A8BA-6F80F5CD1C24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC9B541F-D38C-4E0D-99C2-7CBD45DD5E89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34560" yWindow="2265" windowWidth="21600" windowHeight="11295" tabRatio="861" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="34560" yWindow="2265" windowWidth="21600" windowHeight="11295" tabRatio="861" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="目录导航" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="91">
   <si>
     <t>策划配置表</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -388,6 +388,10 @@
   </si>
   <si>
     <t>负数当底数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>负数不能直接进行非整数次幂运算</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1067,7 +1071,7 @@
         <v>77</v>
       </c>
       <c r="D7" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
